--- a/Team-Data/2008-09/4-12-2008-09.xlsx
+++ b/Team-Data/2008-09/4-12-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -769,13 +836,13 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -793,13 +860,13 @@
         <v>19</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -811,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -846,25 +913,25 @@
         <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.747</v>
+        <v>0.759</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -873,16 +940,16 @@
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="O3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -891,19 +958,19 @@
         <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -912,16 +979,16 @@
         <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -948,7 +1015,7 @@
         <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -957,10 +1024,10 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1124,13 +1191,13 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN4" t="n">
         <v>14</v>
@@ -1148,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1157,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
@@ -1240,64 +1307,64 @@
         <v>0.384</v>
       </c>
       <c r="O5" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF5" t="n">
         <v>16</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,19 +1373,19 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
         <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1327,7 +1394,7 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
         <v>15</v>
@@ -1342,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1351,7 +1418,7 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -1392,34 +1459,34 @@
         <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.823</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
         <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
         <v>18.5</v>
@@ -1437,22 +1504,22 @@
         <v>31.4</v>
       </c>
       <c r="T6" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
         <v>12.6</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.1</v>
@@ -1461,13 +1528,13 @@
         <v>20.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1491,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1503,10 +1570,10 @@
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1515,10 +1582,10 @@
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
@@ -1530,7 +1597,7 @@
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
         <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.608</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K7" t="n">
         <v>0.462</v>
@@ -1601,16 +1668,16 @@
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
         <v>18.5</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11.2</v>
@@ -1643,22 +1710,22 @@
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
         <v>14</v>
@@ -1673,19 +1740,19 @@
         <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ7" t="n">
         <v>2</v>
@@ -1703,19 +1770,19 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
       </c>
       <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4</v>
       </c>
       <c r="BA7" t="n">
         <v>24</v>
@@ -1724,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>10</v>
@@ -1876,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2025,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2073,13 +2140,13 @@
         <v>29</v>
       </c>
       <c r="AX9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>19</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>18</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2249,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>24</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
@@ -2571,7 +2638,7 @@
         <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2592,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
         <v>24</v>
@@ -2613,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
         <v>23</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2771,13 +2838,13 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2930,7 @@
         <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,13 +2939,13 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P14" t="n">
         <v>25.6</v>
@@ -2893,13 +2960,13 @@
         <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
@@ -2914,16 +2981,16 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.8</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2950,10 +3017,10 @@
         <v>16</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>11</v>
@@ -2980,19 +3047,19 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>15</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>16</v>
-      </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3094,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
         <v>13.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O15" t="n">
         <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S15" t="n">
         <v>28.4</v>
@@ -3081,7 +3148,7 @@
         <v>17.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
         <v>7.5</v>
@@ -3099,19 +3166,19 @@
         <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
@@ -3123,7 +3190,7 @@
         <v>30</v>
       </c>
       <c r="AJ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
@@ -3135,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3162,16 +3229,16 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.525</v>
+        <v>0.519</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J16" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
         <v>17.4</v>
@@ -3248,16 +3315,16 @@
         <v>23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R16" t="n">
         <v>10</v>
       </c>
       <c r="S16" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
@@ -3266,10 +3333,10 @@
         <v>12.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
         <v>4.1</v>
@@ -3278,16 +3345,16 @@
         <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3299,25 +3366,25 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM16" t="n">
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
@@ -3350,19 +3417,19 @@
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
         <v>33</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.418</v>
+        <v>0.413</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,7 +3479,7 @@
         <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>6.2</v>
@@ -3421,25 +3488,25 @@
         <v>17.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
         <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>11.8</v>
       </c>
       <c r="S17" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U17" t="n">
         <v>21.8</v>
@@ -3457,19 +3524,19 @@
         <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3505,7 +3572,7 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,7 +3581,7 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3523,10 +3590,10 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3541,10 +3608,10 @@
         <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3678,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>25</v>
@@ -3693,7 +3760,7 @@
         <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>18</v>
@@ -3702,13 +3769,13 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>28</v>
@@ -3717,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3833,31 +3900,31 @@
         <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
@@ -3893,10 +3960,10 @@
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.613</v>
+        <v>0.608</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J20" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
@@ -3970,25 +4037,25 @@
         <v>0.365</v>
       </c>
       <c r="O20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
@@ -4009,13 +4076,13 @@
         <v>20.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4027,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>13</v>
@@ -4051,13 +4118,13 @@
         <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
@@ -4066,7 +4133,7 @@
         <v>25</v>
       </c>
       <c r="AU20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="n">
         <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.383</v>
+        <v>0.388</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4149,7 +4216,7 @@
         <v>27.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O21" t="n">
         <v>18.2</v>
@@ -4158,22 +4225,22 @@
         <v>23.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R21" t="n">
         <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T21" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
         <v>7.4</v>
@@ -4185,16 +4252,16 @@
         <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.2</v>
+        <v>105.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
@@ -4203,13 +4270,13 @@
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4245,25 +4312,25 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4391,10 +4458,10 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4415,7 +4482,7 @@
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4430,13 +4497,13 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4686,7 +4753,7 @@
         <v>79.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
@@ -4695,25 +4762,25 @@
         <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.319</v>
+        <v>0.318</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P24" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R24" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S24" t="n">
         <v>28.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
         <v>20.1</v>
@@ -4725,25 +4792,25 @@
         <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>20.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4761,10 +4828,10 @@
         <v>17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4794,10 +4861,10 @@
         <v>17</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -4818,7 +4885,7 @@
         <v>22</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4991,7 +5058,7 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
         <v>52</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
         <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5083,7 +5150,7 @@
         <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5098,22 +5165,22 @@
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
         <v>6</v>
@@ -5143,10 +5210,10 @@
         <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,13 +5225,13 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5173,10 +5240,10 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5241,16 +5308,16 @@
         <v>19.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="R27" t="n">
         <v>10.3</v>
@@ -5259,13 +5326,13 @@
         <v>28.8</v>
       </c>
       <c r="T27" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U27" t="n">
         <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.9</v>
@@ -5280,16 +5347,16 @@
         <v>23.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
         <v>11</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5334,13 +5401,13 @@
         <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>29</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
         <v>26</v>
@@ -5355,10 +5422,10 @@
         <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F28" t="n">
         <v>28</v>
       </c>
       <c r="G28" t="n">
-        <v>0.65</v>
+        <v>0.646</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
@@ -5429,19 +5496,19 @@
         <v>15.2</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U28" t="n">
         <v>21.2</v>
@@ -5471,22 +5538,22 @@
         <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF28" t="n">
         <v>6</v>
       </c>
-      <c r="AF28" t="n">
-        <v>7</v>
-      </c>
       <c r="AG28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>21</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>0.388</v>
+        <v>0.38</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5596,7 +5663,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
@@ -5605,25 +5672,25 @@
         <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P29" t="n">
         <v>22.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="R29" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
         <v>22.2</v>
@@ -5632,37 +5699,37 @@
         <v>13.4</v>
       </c>
       <c r="W29" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA29" t="n">
         <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>14</v>
@@ -5674,22 +5741,22 @@
         <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN29" t="n">
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>21</v>
@@ -5710,10 +5777,10 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
@@ -5847,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -5892,7 +5959,7 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX30" t="n">
         <v>21</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6068,25 +6135,25 @@
         <v>23</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
       </c>
       <c r="AY31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-12-2008-09</t>
+          <t>2009-04-12</t>
         </is>
       </c>
     </row>
